--- a/reports/risk_summary_report.xlsx
+++ b/reports/risk_summary_report.xlsx
@@ -10,7 +10,6 @@
     <sheet name="Portfolio Metrics" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Risks by Product" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ML Feature Importance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Model Governance" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -790,40 +789,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Pass - Compliant</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2977</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/reports/risk_summary_report.xlsx
+++ b/reports/risk_summary_report.xlsx
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44764381.17567678</v>
+        <v>44626193.79379303</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45129552.48646582</v>
+        <v>44831206.41361938</v>
       </c>
     </row>
     <row r="4">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.65814783193417</v>
+        <v>2.666378928031055</v>
       </c>
     </row>
     <row r="5">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>265.814783193417</v>
+        <v>266.6378928031055</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9977301764978574</v>
+        <v>0.9979534841649423</v>
       </c>
     </row>
     <row r="7">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01399476453661919</v>
+        <v>0.01348675787448883</v>
       </c>
     </row>
   </sheetData>
@@ -552,10 +552,10 @@
         <v>5.47505244242807</v>
       </c>
       <c r="E2" t="n">
-        <v>4.342650952017712</v>
+        <v>4.361926462023122</v>
       </c>
       <c r="F2" t="n">
-        <v>5.299173889080774</v>
+        <v>5.203403990036204</v>
       </c>
     </row>
     <row r="3">
@@ -574,10 +574,10 @@
         <v>3.877120891187244</v>
       </c>
       <c r="E3" t="n">
-        <v>4.162759811866636</v>
+        <v>4.203636270842431</v>
       </c>
       <c r="F3" t="n">
-        <v>5.381319296724539</v>
+        <v>5.364867078345162</v>
       </c>
     </row>
     <row r="4">
@@ -596,10 +596,10 @@
         <v>6.091241143731888</v>
       </c>
       <c r="E4" t="n">
-        <v>4.349412977528829</v>
+        <v>4.347224991920704</v>
       </c>
       <c r="F4" t="n">
-        <v>5.325401742037355</v>
+        <v>5.315157096071462</v>
       </c>
     </row>
     <row r="5">
@@ -618,10 +618,10 @@
         <v>3.474342866036952</v>
       </c>
       <c r="E5" t="n">
-        <v>4.255562229093446</v>
+        <v>4.307162532296616</v>
       </c>
       <c r="F5" t="n">
-        <v>5.311374883809972</v>
+        <v>5.297408604459279</v>
       </c>
     </row>
     <row r="6">
@@ -640,10 +640,10 @@
         <v>4.494660689508277</v>
       </c>
       <c r="E6" t="n">
-        <v>4.232550816673212</v>
+        <v>4.284532010358539</v>
       </c>
       <c r="F6" t="n">
-        <v>5.306420032070194</v>
+        <v>5.276367645003185</v>
       </c>
     </row>
     <row r="7">
@@ -662,10 +662,10 @@
         <v>2.419253194704907</v>
       </c>
       <c r="E7" t="n">
-        <v>4.29624465318241</v>
+        <v>4.345049114069802</v>
       </c>
       <c r="F7" t="n">
-        <v>5.441344249109669</v>
+        <v>5.2641025390289</v>
       </c>
     </row>
     <row r="8">
@@ -684,10 +684,10 @@
         <v>3.824239977161246</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3501823261668</v>
+        <v>4.094653044167726</v>
       </c>
       <c r="F8" t="n">
-        <v>5.226761508213476</v>
+        <v>5.119213478760006</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.620244026184082</v>
+        <v>0.6298132538795471</v>
       </c>
     </row>
     <row r="3">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3024180233478546</v>
+        <v>0.2954300343990326</v>
       </c>
     </row>
     <row r="4">
@@ -743,27 +743,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04529191181063652</v>
+        <v>0.04084992036223412</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Operational_Risk</t>
+          <t>Market_Risk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009511284530162811</v>
+        <v>0.01039435900747776</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Market_Risk</t>
+          <t>Operational_Risk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008323761634528637</v>
+        <v>0.008897897787392139</v>
       </c>
     </row>
     <row r="7">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007630395237356424</v>
+        <v>0.007458833511918783</v>
       </c>
     </row>
     <row r="8">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006580637767910957</v>
+        <v>0.007155647501349449</v>
       </c>
     </row>
   </sheetData>

--- a/reports/risk_summary_report.xlsx
+++ b/reports/risk_summary_report.xlsx
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44690948.54481202</v>
+        <v>44702079.31240095</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45104952.27453943</v>
+        <v>44942620.1339686</v>
       </c>
     </row>
     <row r="4">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.662515490148688</v>
+        <v>2.661852526779229</v>
       </c>
     </row>
     <row r="5">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>266.2515490148688</v>
+        <v>266.1852526779229</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9982926856845652</v>
+        <v>0.9988862883439052</v>
       </c>
     </row>
     <row r="7">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01391142606735229</v>
+        <v>0.01372612547129393</v>
       </c>
     </row>
   </sheetData>
@@ -552,10 +552,10 @@
         <v>5.47505244242807</v>
       </c>
       <c r="E2" t="n">
-        <v>4.460435789892159</v>
+        <v>4.217095893332942</v>
       </c>
       <c r="F2" t="n">
-        <v>5.24406922412883</v>
+        <v>5.285190094700254</v>
       </c>
     </row>
     <row r="3">
@@ -574,10 +574,10 @@
         <v>3.877120891187244</v>
       </c>
       <c r="E3" t="n">
-        <v>4.196620746756418</v>
+        <v>4.137662937906698</v>
       </c>
       <c r="F3" t="n">
-        <v>5.394565056106587</v>
+        <v>5.421130854100031</v>
       </c>
     </row>
     <row r="4">
@@ -596,10 +596,10 @@
         <v>6.091241143731888</v>
       </c>
       <c r="E4" t="n">
-        <v>4.253268039441625</v>
+        <v>4.156444264019331</v>
       </c>
       <c r="F4" t="n">
-        <v>5.280544611895009</v>
+        <v>5.342730557285626</v>
       </c>
     </row>
     <row r="5">
@@ -618,10 +618,10 @@
         <v>3.474342866036952</v>
       </c>
       <c r="E5" t="n">
-        <v>4.23482579052373</v>
+        <v>4.17164387245862</v>
       </c>
       <c r="F5" t="n">
-        <v>5.381799278591024</v>
+        <v>5.364771642114882</v>
       </c>
     </row>
     <row r="6">
@@ -640,10 +640,10 @@
         <v>4.494660689508277</v>
       </c>
       <c r="E6" t="n">
-        <v>4.250065288889567</v>
+        <v>4.237314661921834</v>
       </c>
       <c r="F6" t="n">
-        <v>5.397817129295025</v>
+        <v>5.309275902572131</v>
       </c>
     </row>
     <row r="7">
@@ -662,10 +662,10 @@
         <v>2.419253194704907</v>
       </c>
       <c r="E7" t="n">
-        <v>4.426556987532945</v>
+        <v>4.135198091531637</v>
       </c>
       <c r="F7" t="n">
-        <v>5.409446822850214</v>
+        <v>5.432896655319399</v>
       </c>
     </row>
     <row r="8">
@@ -684,10 +684,10 @@
         <v>3.824239977161246</v>
       </c>
       <c r="E8" t="n">
-        <v>4.844914623140179</v>
+        <v>3.59418831102955</v>
       </c>
       <c r="F8" t="n">
-        <v>5.215845142480132</v>
+        <v>4.833821398365877</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6118179559707642</v>
+        <v>0.6245895624160767</v>
       </c>
     </row>
     <row r="3">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3119166493415833</v>
+        <v>0.2991340458393097</v>
       </c>
     </row>
     <row r="4">
@@ -743,37 +743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04496497288346291</v>
+        <v>0.04505334049463272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Market_Risk</t>
+          <t>Operational_Risk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009291271679103374</v>
+        <v>0.009529310278594494</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Credit_Risk</t>
+          <t>Market_Risk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008198070339858532</v>
+        <v>0.008225406520068645</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Operational_Risk</t>
+          <t>Credit_Risk</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.006927839946001768</v>
+        <v>0.008081872016191483</v>
       </c>
     </row>
     <row r="8">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006883241701871157</v>
+        <v>0.005386462900787592</v>
       </c>
     </row>
   </sheetData>
